--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487871_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487871_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0966</v>
+        <v>6.1054</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0776</v>
+        <v>4.2919</v>
       </c>
       <c r="F2" t="n">
-        <v>2.019</v>
+        <v>1.8135</v>
       </c>
       <c r="G2" t="n">
         <v>3.1186</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0032</v>
+        <v>0.0056</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3138</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3106</v>
+        <v>0.1051</v>
       </c>
       <c r="V2" t="n">
         <v>2.565</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.372</v>
+        <v>3.5858</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8389</v>
+        <v>1.5137</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5331</v>
+        <v>2.0721</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1797</v>
+        <v>3.7031</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9659</v>
+        <v>2.8017</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7862</v>
+        <v>0.9013</v>
       </c>
       <c r="J3" t="n">
-        <v>2.535</v>
+        <v>3.491</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5048</v>
+        <v>3.6266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0302</v>
+        <v>-0.1355</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3554</v>
+        <v>0.212</v>
       </c>
       <c r="N3" t="n">
-        <v>0.461</v>
+        <v>-0.8248</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8164</v>
+        <v>1.0369</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0189</v>
+        <v>-0.9497</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0562</v>
+        <v>-0.9367</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0372</v>
+        <v>-0.013</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4412</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.097</v>
+        <v>3.2457</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4066</v>
+        <v>2.6246</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6904</v>
+        <v>0.6212</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7031</v>
+        <v>2.1797</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8017</v>
+        <v>2.9659</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9013</v>
+        <v>-0.7862</v>
       </c>
       <c r="J4" t="n">
-        <v>3.491</v>
+        <v>2.535</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6266</v>
+        <v>2.5048</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1355</v>
+        <v>0.0302</v>
       </c>
       <c r="M4" t="n">
-        <v>0.212</v>
+        <v>-0.3554</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8248</v>
+        <v>0.461</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0369</v>
+        <v>-0.8164</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4386</v>
+        <v>-0.1451</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0439</v>
+        <v>-0.2705</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3947</v>
+        <v>0.1253</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.4412</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8162</v>
+        <v>3.1964</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0984</v>
+        <v>0.2231</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9146</v>
+        <v>2.9733</v>
       </c>
       <c r="G5" t="n">
         <v>-2.1266</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.871</v>
+        <v>-0.4908</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.423</v>
+        <v>-1.1015</v>
       </c>
       <c r="U5" t="n">
-        <v>0.552</v>
+        <v>0.6107</v>
       </c>
       <c r="V5" t="n">
         <v>3.7325</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7604</v>
+        <v>2.1571</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0408</v>
+        <v>2.2907</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2803</v>
+        <v>-0.1335</v>
       </c>
       <c r="G6" t="n">
         <v>0.8856000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5637</v>
+        <v>-0.0396</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6458</v>
+        <v>-0.1043</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0822</v>
+        <v>0.0646</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3538</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5442</v>
+        <v>1.4268</v>
       </c>
       <c r="E7" t="n">
         <v>0.456</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0882</v>
+        <v>0.9708</v>
       </c>
       <c r="G7" t="n">
         <v>2.7003</v>
@@ -1000,13 +1000,13 @@
         <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3008</v>
+        <v>0.1833</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4313</v>
+        <v>0.3138</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7433</v>
+        <v>1.0164</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4323</v>
+        <v>1.6466</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6303</v>
       </c>
       <c r="G8" t="n">
         <v>1.1982</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6224</v>
+        <v>-0.3493</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.64</v>
+        <v>-0.4257</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0177</v>
+        <v>0.0764</v>
       </c>
       <c r="V8" t="n">
         <v>0.5838</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7612</v>
+        <v>-0.2137</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2725</v>
+        <v>1.3796</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0337</v>
+        <v>-1.5933</v>
       </c>
       <c r="G9" t="n">
         <v>1.0227</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8651</v>
+        <v>-0.3175</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4443</v>
+        <v>-0.3372</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4208</v>
+        <v>0.0196</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7513</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.084</v>
+        <v>-4.1189</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3242</v>
+        <v>-3.8076</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2403</v>
+        <v>-0.3114</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8381</v>
+        <v>-1.0873</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.038</v>
+        <v>-1.4497</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8001</v>
+        <v>0.3625</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8173</v>
+        <v>-0.9687</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5845</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2328</v>
+        <v>-0.3886</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0208</v>
+        <v>-0.1186</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4535</v>
+        <v>-0.8697</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4327</v>
+        <v>0.7511</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4162</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1516</v>
+        <v>-0.6997</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.6338</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8073</v>
+        <v>-0.0659</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.9813</v>
+        <v>-1.2914</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>-0.1238</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2112</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5975</v>
+        <v>-4.4139</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0219</v>
+        <v>-4.5385</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5756</v>
+        <v>0.1246</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0873</v>
+        <v>-1.8381</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4497</v>
+        <v>-1.038</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3625</v>
+        <v>-0.8001</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9687</v>
+        <v>-1.8173</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5845</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3886</v>
+        <v>-1.2328</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1186</v>
+        <v>-0.0208</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8697</v>
+        <v>-0.4535</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7511</v>
+        <v>0.4327</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1783</v>
+        <v>-0.1784</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8482</v>
+        <v>-0.87</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3301</v>
+        <v>0.6917</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2914</v>
+        <v>-1.9813</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1238</v>
+        <v>0.23</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1675</v>
+        <v>-2.2112</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.987</v>
+        <v>11.9871</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0802</v>
+        <v>6.080100000000001</v>
       </c>
       <c r="F12" t="n">
         <v>5.907</v>
@@ -1360,25 +1360,25 @@
         <v>9.0418</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7142999999999999</v>
+        <v>0.7143000000000002</v>
       </c>
       <c r="J12" t="n">
         <v>9.982800000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>8.941899999999999</v>
+        <v>8.9419</v>
       </c>
       <c r="L12" t="n">
-        <v>1.041</v>
+        <v>1.041000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2267000000000003</v>
+        <v>-0.2267000000000002</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09970000000000001</v>
+        <v>0.09970000000000023</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3264000000000001</v>
+        <v>-0.3264000000000002</v>
       </c>
       <c r="P12" t="n">
         <v>2.0813</v>
@@ -1390,16 +1390,16 @@
         <v>13.5277</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.9814</v>
+        <v>-2.9812</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.909800000000001</v>
+        <v>-4.9097</v>
       </c>
       <c r="U12" t="n">
         <v>1.9283</v>
       </c>
       <c r="V12" t="n">
-        <v>3.130999999999999</v>
+        <v>3.130999999999998</v>
       </c>
       <c r="W12" t="n">
         <v>12.4536</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6881</v>
+        <v>3.9024</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0496</v>
+        <v>3.2639</v>
       </c>
       <c r="F13" t="n">
         <v>0.6384</v>
@@ -1468,10 +1468,10 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5715</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0215</v>
+        <v>0.2358</v>
       </c>
       <c r="U13" t="n">
         <v>0.55</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3672</v>
+        <v>1.2664</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2651</v>
+        <v>1.0508</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1021</v>
+        <v>0.2156</v>
       </c>
       <c r="G14" t="n">
         <v>-1.2425</v>
@@ -1546,13 +1546,13 @@
         <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3562</v>
+        <v>0.2554</v>
       </c>
       <c r="T14" t="n">
-        <v>0.152</v>
+        <v>-0.0624</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2042</v>
+        <v>0.3178</v>
       </c>
       <c r="V14" t="n">
         <v>1.0048</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8874</v>
+        <v>1.1286</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1991</v>
+        <v>-0.3063</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0865</v>
+        <v>1.4349</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3231</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0216</v>
+        <v>0.2197</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5657</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5442</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>3.2726</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.668</v>
+        <v>1.1069</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8835</v>
+        <v>1.205</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2155</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-2.7503</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1703</v>
+        <v>0.2686</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1057</v>
+        <v>0.2158</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0646</v>
+        <v>0.0529</v>
       </c>
       <c r="V16" t="n">
         <v>2.7561</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1468</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8555</v>
+        <v>2.3913</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7087</v>
+        <v>-1.5913</v>
       </c>
       <c r="G17" t="n">
         <v>2.9721</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4684</v>
+        <v>0.1848</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0967</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6283</v>
+        <v>0.7458</v>
       </c>
       <c r="V17" t="n">
         <v>-2.565</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4409</v>
+        <v>-0.3337</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="F18" t="n">
         <v>-0.3756</v>
@@ -1858,10 +1858,10 @@
         <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2027</v>
+        <v>-1.2717</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7286</v>
+        <v>-1.6215</v>
       </c>
       <c r="F19" t="n">
-        <v>0.526</v>
+        <v>0.3498</v>
       </c>
       <c r="G19" t="n">
         <v>0.5886</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4169</v>
+        <v>0.3479</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4443</v>
+        <v>-0.3372</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8612</v>
+        <v>0.6851</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1675</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4504</v>
+        <v>-2.2543</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2295</v>
+        <v>-1.7652</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2209</v>
+        <v>-0.4891</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4796</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0681</v>
+        <v>1.2642</v>
       </c>
       <c r="T20" t="n">
-        <v>1.323</v>
+        <v>0.7873</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7451</v>
+        <v>0.4769</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7902</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. CHABI YO</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4365</v>
+        <v>-2.5219</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5702</v>
+        <v>-3.818</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8663</v>
+        <v>1.2961</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9224</v>
+        <v>-2.9304</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3966</v>
+        <v>-2.9068</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5258</v>
+        <v>-0.0237</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2161</v>
+        <v>-2.1016</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2944</v>
+        <v>-2.18</v>
       </c>
       <c r="L21" t="n">
         <v>0.0784</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7063</v>
+        <v>-0.8289</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1022</v>
+        <v>-0.7268</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6041</v>
+        <v>-0.102</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.927</v>
+        <v>-0.0295</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6458</v>
+        <v>-0.9058</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2812</v>
+        <v>0.8762</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8574</v>
+        <v>0.23</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>S. CHABI YO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8433</v>
+        <v>-2.7898</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1394</v>
+        <v>-1.2132</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2961</v>
+        <v>-1.5766</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9304</v>
+        <v>-1.9224</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.9068</v>
+        <v>-1.3966</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0237</v>
+        <v>-0.5258</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1016</v>
+        <v>-1.2161</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.18</v>
+        <v>-1.2944</v>
       </c>
       <c r="L22" t="n">
         <v>0.0784</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8289</v>
+        <v>-0.7063</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7268</v>
+        <v>-0.1022</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.102</v>
+        <v>-0.6041</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.351</v>
+        <v>0.5738</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2272</v>
+        <v>0.0029</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8762</v>
+        <v>0.5709</v>
       </c>
       <c r="V22" t="n">
-        <v>0.23</v>
+        <v>-1.8574</v>
       </c>
       <c r="W22" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.8574</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4113</v>
+        <v>-3.0629</v>
       </c>
       <c r="E23" t="n">
         <v>-1.9436</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4677</v>
+        <v>-1.1193</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3121</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7235</v>
+        <v>-0.3751</v>
       </c>
       <c r="T23" t="n">
         <v>-0.7177</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0059</v>
+        <v>0.3425</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9593</v>
+        <v>-7.2427</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0849</v>
+        <v>-3.1921</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8744</v>
+        <v>-4.0506</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7575</v>
@@ -2326,13 +2326,13 @@
         <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4417</v>
+        <v>0.1584</v>
       </c>
       <c r="T24" t="n">
-        <v>0.152</v>
+        <v>0.0448</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2897</v>
+        <v>0.1136</v>
       </c>
       <c r="V24" t="n">
         <v>-4.0191</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.9869</v>
+        <v>-11.2727</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9068</v>
+        <v>-5.907</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.08</v>
+        <v>-5.3658</v>
       </c>
       <c r="G25" t="n">
         <v>-9.7561</v>
@@ -2404,13 +2404,13 @@
         <v>11.4465</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9814</v>
+        <v>3.6959</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.9282</v>
+        <v>-1.9285</v>
       </c>
       <c r="U25" t="n">
-        <v>4.9096</v>
+        <v>5.6243</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1309</v>
